--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125560846</v>
+        <v>125561045</v>
       </c>
       <c r="B2" t="n">
-        <v>78947</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604052</v>
+        <v>604053</v>
       </c>
       <c r="R2" t="n">
-        <v>6936962</v>
+        <v>6936941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125561045</v>
+        <v>125565960</v>
       </c>
       <c r="B3" t="n">
-        <v>80028</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +793,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604053</v>
+        <v>604167</v>
       </c>
       <c r="R3" t="n">
-        <v>6936941</v>
+        <v>6936934</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125565560</v>
+        <v>125560846</v>
       </c>
       <c r="B4" t="n">
-        <v>97147</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +901,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604133</v>
+        <v>604052</v>
       </c>
       <c r="R4" t="n">
-        <v>6936936</v>
+        <v>6936962</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1093,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125565960</v>
+        <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>57635</v>
+        <v>97147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1105,43 +1115,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604167</v>
+        <v>604133</v>
       </c>
       <c r="R6" t="n">
-        <v>6936934</v>
+        <v>6936936</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,11 +1179,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125561045</v>
+        <v>125565960</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604053</v>
+        <v>604167</v>
       </c>
       <c r="R2" t="n">
-        <v>6936941</v>
+        <v>6936934</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125565960</v>
+        <v>125561045</v>
       </c>
       <c r="B3" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604167</v>
+        <v>604053</v>
       </c>
       <c r="R3" t="n">
-        <v>6936934</v>
+        <v>6936941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,12 +882,7 @@
         <v>125560846</v>
       </c>
       <c r="B4" t="n">
-        <v>78947</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78967</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,12 +979,7 @@
         <v>125566159</v>
       </c>
       <c r="B5" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1106,12 +1086,7 @@
         <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -976,50 +976,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125566159</v>
+        <v>125565560</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>97202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604069</v>
+        <v>604133</v>
       </c>
       <c r="R5" t="n">
-        <v>6936885</v>
+        <v>6936936</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1052,11 +1047,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,45 +1073,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125565560</v>
+        <v>125566159</v>
       </c>
       <c r="B6" t="n">
-        <v>97202</v>
+        <v>57651</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604133</v>
+        <v>604069</v>
       </c>
       <c r="R6" t="n">
-        <v>6936936</v>
+        <v>6936885</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,6 +1149,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -976,45 +976,50 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125565560</v>
+        <v>125566159</v>
       </c>
       <c r="B5" t="n">
-        <v>97202</v>
+        <v>57651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604133</v>
+        <v>604069</v>
       </c>
       <c r="R5" t="n">
-        <v>6936936</v>
+        <v>6936885</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1047,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1073,50 +1083,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125566159</v>
+        <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>57651</v>
+        <v>97209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604069</v>
+        <v>604133</v>
       </c>
       <c r="R6" t="n">
-        <v>6936885</v>
+        <v>6936936</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1149,11 +1154,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125561045</v>
       </c>
       <c r="B3" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125560846</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>125561045</v>
       </c>
       <c r="B3" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125560846</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>97212</v>
+        <v>97216</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>97216</v>
+        <v>97217</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125565960</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>125561045</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>125560846</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125566159</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1086,7 +1086,7 @@
         <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>97219</v>
+        <v>97221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -1086,7 +1086,7 @@
         <v>125565560</v>
       </c>
       <c r="B6" t="n">
-        <v>97221</v>
+        <v>97223</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125565960</v>
       </c>
       <c r="B2" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125566159</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1178,6 +1178,214 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129925017</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>604082</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6936930</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129925181</v>
+      </c>
+      <c r="B8" t="n">
+        <v>75193</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>604126</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6936976</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125565960</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>125566159</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1183,7 +1183,7 @@
         <v>129925017</v>
       </c>
       <c r="B7" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>129925181</v>
       </c>
       <c r="B8" t="n">
-        <v>75193</v>
+        <v>75196</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -1183,7 +1183,7 @@
         <v>129925017</v>
       </c>
       <c r="B7" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>129925181</v>
       </c>
       <c r="B8" t="n">
-        <v>75201</v>
+        <v>75286</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125565960</v>
+        <v>125560846</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>604167</v>
+        <v>604052</v>
       </c>
       <c r="R2" t="n">
-        <v>6936934</v>
+        <v>6936962</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125561045</v>
+        <v>129925181</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>75428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6426</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>604053</v>
+        <v>604126</v>
       </c>
       <c r="R3" t="n">
-        <v>6936941</v>
+        <v>6936976</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +840,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-31</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -861,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -879,10 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125560846</v>
+        <v>125561045</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +884,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +908,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>604052</v>
+        <v>604053</v>
       </c>
       <c r="R4" t="n">
-        <v>6936962</v>
+        <v>6936941</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -976,10 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125566159</v>
+        <v>125565330</v>
       </c>
       <c r="B5" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,7 +1001,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1016,10 +1010,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>604069</v>
+        <v>604005</v>
       </c>
       <c r="R5" t="n">
-        <v>6936885</v>
+        <v>6936979</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,45 +1077,50 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125565560</v>
+        <v>125565383</v>
       </c>
       <c r="B6" t="n">
-        <v>97223</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>604133</v>
+        <v>604000</v>
       </c>
       <c r="R6" t="n">
-        <v>6936936</v>
+        <v>6936964</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1154,6 +1153,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1180,10 +1184,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129925017</v>
+        <v>125565960</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,7 +1215,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1220,10 +1224,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>604082</v>
+        <v>604167</v>
       </c>
       <c r="R7" t="n">
-        <v>6936930</v>
+        <v>6936934</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,12 +1254,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1287,48 +1291,50 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129925181</v>
+        <v>125566159</v>
       </c>
       <c r="B8" t="n">
-        <v>75286</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6426</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Lill-Rödmyran, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>604126</v>
+        <v>604069</v>
       </c>
       <c r="R8" t="n">
-        <v>6936976</v>
+        <v>6936885</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1355,12 +1361,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1369,7 +1380,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1385,6 +1395,210 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129925017</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>604082</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6936930</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>125565560</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lill-Rödmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>604133</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6936936</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24422-2025 artfynd.xlsx
+++ b/artfynd/A 24422-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125560846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129925181</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125561045</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565330</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1181,6 +1206,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565383</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1288,6 +1318,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565960</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1395,6 +1430,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125566159</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1502,6 +1542,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129925017</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1599,8 +1644,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125565560</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>